--- a/songs/Shivers_v1/quelle/struktur.xlsx
+++ b/songs/Shivers_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>14</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>132</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(6590, 4)   (Matrix: progScrollText("Shivers by Ed Sheeran", 15540, 90, getRandomColor(), 3))</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(6590, 4)   (Matrix: progScrollText("Shivers by Ed Sheeran", 15540, 90, getRandomColor(), 3))</t>
         </is>
@@ -551,13 +566,20 @@
           <t>intro</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlingBlingColoring(29090, 12, 5000)
+! im alten Code ein einziger Part mit den folgenden 1</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(29090, 12, 5000)
 ! im alten Code ein einziger Part mit den folgenden 1</t>
@@ -574,12 +596,13 @@
         </is>
       </c>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -590,13 +613,19 @@
           <t>verse 1b</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(14545, 14, 455, false)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(14545, 14, 455, false)</t>
         </is>
@@ -611,13 +640,19 @@
           <t>i wanna be that guy</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(14545, 4, 16)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progPalette(14545, 4, 16)</t>
         </is>
@@ -632,13 +667,19 @@
           <t>Chorus 1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(14090, 910, 18, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(14090, 910, 18, 5, 26, 5, false, 4)</t>
         </is>
@@ -653,13 +694,19 @@
           <t>mini pause</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(910, 20)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progBlack(910, 20)</t>
         </is>
@@ -674,13 +721,19 @@
           <t>Chorus 1b</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(14090, 8, 22)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14090, 8, 22)</t>
         </is>
@@ -695,13 +748,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(14545, 24, 910)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progFullColors(14545, 24, 910)</t>
         </is>
@@ -716,13 +775,19 @@
           <t>verse 2b</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixScanner(14545, 26, 31)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(14545, 26, 31)</t>
         </is>
@@ -737,13 +802,19 @@
           <t>i wanna be that guy</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(14545, 28, 50, true, true)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(14545, 28, 50, true, true)</t>
         </is>
@@ -758,13 +829,19 @@
           <t>Chorus 1</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(12730, 455, 30, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(12730, 455, 30, 5, 26, 5, true, 3)</t>
         </is>
@@ -779,13 +856,19 @@
           <t>mini pause</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1820, 32, 65, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1820, 32, 65, 255, 255, 255)</t>
         </is>
@@ -800,13 +883,19 @@
           <t>Chorus 1b</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(14545, 8, 34)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14545, 8, 34)</t>
         </is>
@@ -821,13 +910,19 @@
           <t>you burn ….</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(14545, 36)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progBlack(14545, 36)</t>
         </is>
@@ -842,13 +937,19 @@
           <t>you burn …. 2</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(14545, 38, 170, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(14545, 38, 170, 255, 255, 255)</t>
         </is>
@@ -863,13 +964,19 @@
           <t>SOLO VOC</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(3635, 40)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progBlack(3635, 40)</t>
         </is>
@@ -884,13 +991,19 @@
           <t>Chorus 1</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(10000, 910, 42, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(10000, 910, 42, 5, 26, 5, false, 4)</t>
         </is>
@@ -905,13 +1018,19 @@
           <t>mini pause</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(910, 44, 65, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progStrobo(910, 44, 65, 255, 255, 255)</t>
         </is>
@@ -926,13 +1045,19 @@
           <t>Chorus 1b</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(14545, 8, 46)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14545, 8, 46)</t>
         </is>
@@ -952,10 +1077,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/Shivers_v1/quelle/struktur.xlsx
+++ b/songs/Shivers_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>43.75</v>
+        <v>44.75</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>44.25</v>
+        <v>45.25</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>

--- a/songs/Shivers_v1/quelle/struktur.xlsx
+++ b/songs/Shivers_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>132</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +555,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(6590, 4)   (Matrix: progScrollText("Shivers by Ed Sheeran", 15540, 90, getRandomColor(), 3))</t>
         </is>
@@ -574,12 +584,17 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Szene Glow, SUNSET, Farbwanderung (analog, 2 Takte): füllt sich langsam, die Farbe wandert leicht.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(29090, 12, 5000)
 ! im alten Code ein einziger Part mit den folgenden 1</t>
@@ -597,12 +612,17 @@
       </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Szene Verse, SUNSET: dezenter Puls im Beat - Wechsel beim Gesangseinsatz (bisher lief der Intro-Effekt 16 Takte durch).</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -620,12 +640,17 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Szene Call Response, SUNSET: Bühnenhälften blitzen abwechselnd.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(14545, 14, 455, false)</t>
         </is>
@@ -647,12 +672,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Szene Palette, NEON, darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 8 Takte). Letzter halber Takt weißer Strobo (tail 2 Beats). Fester Look für beide.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progPalette(14545, 4, 16)</t>
         </is>
@@ -674,12 +704,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Stern bleibt, in NEON, Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(14090, 910, 18, 5, 26, 5, false, 4)</t>
         </is>
@@ -701,12 +736,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Schwarz bleibt; starker Blinder auf den Wiedereinsatz (Takt 45,25).</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progBlack(910, 20)</t>
         </is>
@@ -728,12 +768,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Einzelblitze bleiben (Szene Sparkle, NEON).</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14090, 8, 22)</t>
         </is>
@@ -755,12 +800,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors, SUNSET, soft 100: die ganze Bühne fließt alle 2 Beats in die nächste Farbe.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progFullColors(14545, 24, 910)</t>
         </is>
@@ -782,12 +832,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Szene Rain, SUNSET, Farbwanderung (triad, 2 Takte).</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(14545, 26, 31)</t>
         </is>
@@ -809,12 +864,17 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>wie beim ersten Mal (Palette NEON + Glitzern, Strobo-Tail) - bisher Wasserringe.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(14545, 28, 50, true, true)</t>
         </is>
@@ -836,12 +896,17 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Stern, NEON, Blinder auf den Einsatz, Lampen blitzen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(12730, 455, 30, 5, 26, 5, true, 3)</t>
         </is>
@@ -863,12 +928,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Weißer Strobo bleibt; Blinder auf den Einsatz von Chorus 1b (Takt 85).</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1820, 32, 65, 255, 255, 255)</t>
         </is>
@@ -890,12 +960,13 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14545, 8, 34)</t>
         </is>
@@ -917,12 +988,17 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Statt 8 Takten Schwarz: Szene Calm, RED, auf 30 % gedimmt - es glimmt nur. (Oder Schwarz lassen, wenn die Stille gewollt ist.)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progBlack(14545, 36)</t>
         </is>
@@ -944,12 +1020,17 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Szene Fire, RED statt 8 Takten Strobo: aus dem Glimmen wird Feuer, blendet über 2 Takte ein (fade_in 8 Beats).</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(14545, 38, 170, 255, 255, 255)</t>
         </is>
@@ -971,12 +1052,17 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Schwarz bleibt (Stille vor dem Finale); in den letzten 2 Beats blendet ein Blinder ein, voll auf dem Chorus-Einsatz (Takt 111).</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progBlack(3635, 40)</t>
         </is>
@@ -998,12 +1084,17 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, FIRE - eine Stufe wärmer.</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(10000, 910, 42, 5, 26, 5, false, 4)</t>
         </is>
@@ -1025,12 +1116,17 @@
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Starker Blinder statt Strobo (2 Beats voll bis zum Einsatz).</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>progStrobo(910, 44, 65, 255, 255, 255)</t>
         </is>
@@ -1052,12 +1148,17 @@
         </is>
       </c>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, FIRE; drei kurze Blinder Ende des 4. Takts (Takt 120,5 / 120,75 / 121); starker Blinder auf der letzten Viertel (Takt 124,75), klingt 5 Sekunden ins Schluss-Schwarz aus (wie APT.).</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14545, 8, 46)</t>
         </is>
@@ -1077,10 +1178,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/Shivers_v1/quelle/struktur.xlsx
+++ b/songs/Shivers_v1/quelle/struktur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="18420" yWindow="3828" windowWidth="27240" windowHeight="20436" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="18420" yWindow="10488" windowWidth="27240" windowHeight="13776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Struktur" sheetId="1" state="visible" r:id="rId1"/>
@@ -2348,7 +2348,7 @@
       <c r="G149" s="5" t="n"/>
       <c r="H149" s="6" t="n"/>
     </row>
-    <row r="150" collapsed="1" ht="28.8" customHeight="1">
+    <row r="150" ht="28.8" customHeight="1">
       <c r="A150" s="4" t="n">
         <v>37</v>
       </c>
@@ -2361,7 +2361,8 @@
         <is>
           <t>SCENE_STAR, Farben SCHEME_NEON
 Ausgabe: Blinder bei 0 ms, 909 ms lang
-Drehender Stern in Neon-Farben, Farbwechsel im Beat. Auf den Einsatz springt ein Blinder auf (warmweiß, alle Geräte) und klingt über 2 Beats ab.</t>
+Schluss (1 Beats): progBlack(455, 10), Farben SCHEME_NEON
+Drehender Stern in Neon-Farben, Farbwechsel im Beat. Auf den Einsatz springt ein Blinder auf (warmweiß, alle Geräte) und klingt über 2 Beats ab. Ab Takt 44,5 ist es schon schwarz.</t>
         </is>
       </c>
       <c r="D150" s="6" t="n"/>
@@ -2377,7 +2378,7 @@
         </is>
       </c>
     </row>
-    <row r="151" hidden="1" outlineLevel="2">
+    <row r="151" outlineLevel="2">
       <c r="A151" s="4" t="n">
         <v>37.25</v>
       </c>
@@ -2389,7 +2390,7 @@
       <c r="G151" s="5" t="n"/>
       <c r="H151" s="6" t="n"/>
     </row>
-    <row r="152" hidden="1" outlineLevel="2">
+    <row r="152" outlineLevel="2">
       <c r="A152" s="4" t="n">
         <v>37.5</v>
       </c>
@@ -2401,7 +2402,7 @@
       <c r="G152" s="5" t="n"/>
       <c r="H152" s="6" t="n"/>
     </row>
-    <row r="153" hidden="1" outlineLevel="2">
+    <row r="153" outlineLevel="2">
       <c r="A153" s="4" t="n">
         <v>37.75</v>
       </c>
@@ -2413,7 +2414,7 @@
       <c r="G153" s="5" t="n"/>
       <c r="H153" s="6" t="n"/>
     </row>
-    <row r="154" hidden="1" outlineLevel="1" collapsed="1">
+    <row r="154" outlineLevel="1" collapsed="1">
       <c r="A154" s="4" t="n">
         <v>38</v>
       </c>
@@ -2461,7 +2462,7 @@
       <c r="G157" s="5" t="n"/>
       <c r="H157" s="6" t="n"/>
     </row>
-    <row r="158" hidden="1" outlineLevel="1" collapsed="1">
+    <row r="158" outlineLevel="1" collapsed="1">
       <c r="A158" s="4" t="n">
         <v>39</v>
       </c>
@@ -2509,7 +2510,7 @@
       <c r="G161" s="5" t="n"/>
       <c r="H161" s="6" t="n"/>
     </row>
-    <row r="162" hidden="1" outlineLevel="1" collapsed="1">
+    <row r="162" outlineLevel="1" collapsed="1">
       <c r="A162" s="4" t="n">
         <v>40</v>
       </c>
@@ -2557,7 +2558,7 @@
       <c r="G165" s="5" t="n"/>
       <c r="H165" s="6" t="n"/>
     </row>
-    <row r="166" hidden="1" outlineLevel="1" collapsed="1">
+    <row r="166" outlineLevel="1" collapsed="1">
       <c r="A166" s="4" t="n">
         <v>41</v>
       </c>
@@ -2605,7 +2606,7 @@
       <c r="G169" s="5" t="n"/>
       <c r="H169" s="6" t="n"/>
     </row>
-    <row r="170" hidden="1" outlineLevel="1" collapsed="1">
+    <row r="170" outlineLevel="1" collapsed="1">
       <c r="A170" s="4" t="n">
         <v>42</v>
       </c>
@@ -2653,7 +2654,7 @@
       <c r="G173" s="5" t="n"/>
       <c r="H173" s="6" t="n"/>
     </row>
-    <row r="174" hidden="1" outlineLevel="1" collapsed="1">
+    <row r="174" outlineLevel="1" collapsed="1">
       <c r="A174" s="4" t="n">
         <v>43</v>
       </c>
@@ -2701,7 +2702,7 @@
       <c r="G177" s="5" t="n"/>
       <c r="H177" s="6" t="n"/>
     </row>
-    <row r="178" hidden="1" outlineLevel="1" collapsed="1">
+    <row r="178" outlineLevel="1">
       <c r="A178" s="4" t="n">
         <v>44</v>
       </c>
@@ -2713,7 +2714,7 @@
       <c r="G178" s="5" t="n"/>
       <c r="H178" s="6" t="n"/>
     </row>
-    <row r="179" hidden="1" outlineLevel="2">
+    <row r="179" outlineLevel="2">
       <c r="A179" s="4" t="n">
         <v>44.25</v>
       </c>
@@ -2725,13 +2726,21 @@
       <c r="G179" s="5" t="n"/>
       <c r="H179" s="6" t="n"/>
     </row>
-    <row r="180" hidden="1" outlineLevel="2">
+    <row r="180" outlineLevel="2">
       <c r="A180" s="4" t="n">
         <v>44.5</v>
       </c>
       <c r="B180" s="5" t="n"/>
-      <c r="C180" s="6" t="n"/>
-      <c r="D180" s="6" t="n"/>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>ab hier schon Schwarz (1 Beat vor der mini pause)</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>ab hier schon progBlack</t>
+        </is>
+      </c>
       <c r="E180" s="6" t="n"/>
       <c r="F180" s="5" t="n"/>
       <c r="G180" s="5" t="n"/>
@@ -2748,9 +2757,9 @@
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>progBlack(909, 10), Farben SCHEME_SUNSET
-Ausgabe: Blinder von 'Chorus 1b' blendet in den letzten 455 ms ein
-2 Beats Schwarz; darin blendet der starke Blinder für den Wiedereinsatz (Takt 45,25) ein.</t>
+          <t>progBlack(909, 11), Farben SCHEME_SUNSET
+Ausgabe: Blinder von 'Chorus 1b' blendet in den letzten 45 ms ein
+2 Beats Schwarz bis zum Wiedereinsatz auf Takt 45,25.</t>
         </is>
       </c>
       <c r="D181" s="6" t="n"/>
@@ -2790,11 +2799,15 @@
       <c r="C183" s="6" t="inlineStr">
         <is>
           <t>SCENE_SPARKLE, Farben SCHEME_NEON
-Ausgabe: Blinder voll bei 0 ms, 1364 ms lang, Blinder blendet in den 455 ms davor ein, 0 ms voll, 909 ms aus
-Schnelle Einzelblitze in Pink, Cyan, Violett. Ein starker Blinder blendet im letzten Beat der Pause ein, ist auf dem Wiedereinsatz voll hell und klingt über 2 Beats ab.</t>
-        </is>
-      </c>
-      <c r="D183" s="6" t="n"/>
+Ausgabe: Blinder voll bei 0 ms, 1409 ms lang, Blinder blendet in den 45 ms davor ein, 0 ms voll, 1364 ms aus
+Schnelle Einzelblitze in Pink, Cyan, Violett. Ein starker Blinder blendet ganz kurz vor dem Wiedereinsatz ein, ist auf Takt 45,25 voll hell und klingt bis Takt 46 (3 Beats) aus.</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>den Blinder erst auf 45,25 -&gt; sehr schnell einblenden und bis 46,0 ausfaden</t>
+        </is>
+      </c>
       <c r="E183" s="6" t="n"/>
       <c r="F183" s="5" t="n"/>
       <c r="G183" s="5">
@@ -3178,7 +3191,7 @@
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>progBeatColors(14545, 12, 132, 2, false), Farben SCHEME_SUNSET
+          <t>progBeatColors(14545, 13, 132, 2, false), Farben SCHEME_SUNSET
 Ausgabe: Farbwechsel weich (100 % des Schritts)
 Die ganze Bühne leuchtet in einer Sunset-Farbe und fließt alle 2 Beats weich in die nächste.</t>
         </is>
@@ -4735,7 +4748,7 @@
       </c>
       <c r="C338" s="6" t="inlineStr">
         <is>
-          <t>progBlack(909, 17), Farben SCHEME_SUNSET
+          <t>progBlack(909, 18), Farben SCHEME_SUNSET
 Schluss (2 Beats): SCENE_COLORS, Farben SCHEME_WHITE
    Ausgabe: Tor 4x pro Beat, 50 % hell
 2 Beats Schwarz, ab Takt 84,5 weißer Strobo im Takt (4 Blitze pro Beat) auf allen Geräten.</t>
@@ -4776,11 +4789,7 @@
           <t>erst hier der weiße Strobo (4 Blitze pro Beat), davor 2 Beats Schwarz</t>
         </is>
       </c>
-      <c r="D340" s="6" t="inlineStr">
-        <is>
-          <t>hier erst der strobo</t>
-        </is>
-      </c>
+      <c r="D340" s="6" t="n"/>
       <c r="E340" s="6" t="n"/>
       <c r="F340" s="5" t="n"/>
       <c r="G340" s="5" t="n"/>
@@ -4827,7 +4836,7 @@
         </is>
       </c>
     </row>
-    <row r="343" outlineLevel="2">
+    <row r="343" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A343" s="4" t="n">
         <v>85.25</v>
       </c>
@@ -4837,11 +4846,7 @@
           <t>Höhepunkt des Blinders erst hier: blendet ab Takt 85 über 1 Beat ein, klingt danach über 2 Beats ab</t>
         </is>
       </c>
-      <c r="D343" s="6" t="inlineStr">
-        <is>
-          <t>hier erst höhepunkt des Blinders</t>
-        </is>
-      </c>
+      <c r="D343" s="6" t="n"/>
       <c r="E343" s="6" t="n"/>
       <c r="F343" s="5" t="n"/>
       <c r="G343" s="5" t="n"/>
@@ -6022,16 +6027,12 @@
         <is>
           <t>SCENE_FIRE, Farben SCHEME_RED
 Ausgabe: Übergang fade 455 ms, blendet die letzten 1818 ms aus
-Schluss (4 Beats): progBlack(1818, 23), Farben SCHEME_RED
+Schluss (4 Beats): progBlack(1818, 24), Farben SCHEME_RED
    Ausgabe: Blinder von 'Chorus 1 (3)' blendet in den letzten 909 ms ein
 Das rote Feuer aus 'you burn' blendet ganz langsam über einen Takt nach Schwarz aus, danach Stille; in den letzten 2 Beats blendet ein Blinder ein, voll hell auf dem Chorus-Einsatz (Takt 111).</t>
         </is>
       </c>
-      <c r="D438" s="6" t="inlineStr">
-        <is>
-          <t>hier bitte ganz langsam den ausfaden  über einen takt</t>
-        </is>
-      </c>
+      <c r="D438" s="6" t="n"/>
       <c r="E438" s="6" t="n"/>
       <c r="F438" s="5" t="n"/>
       <c r="G438" s="5">
@@ -6409,7 +6410,7 @@
       <c r="G467" s="5" t="n"/>
       <c r="H467" s="6" t="n"/>
     </row>
-    <row r="468" collapsed="1" ht="28.8" customHeight="1">
+    <row r="468" ht="28.8" customHeight="1">
       <c r="A468" s="4" t="n">
         <v>116.5</v>
       </c>
@@ -6420,7 +6421,7 @@
       </c>
       <c r="C468" s="6" t="inlineStr">
         <is>
-          <t>progBlack(1364, 25), Farben SCHEME_SUNSET
+          <t>progBlack(1364, 26), Farben SCHEME_SUNSET
 Ausgabe: Blinder bei 0 ms, 1364 ms lang, Blinder blendet 0 ms ein, 1318 ms voll, 46 ms aus
 Starker Blinder (warmweiß, alle Geräte) steht die ganzen 3 Beats voll bis zum Einsatz auf Takt 117,25.</t>
         </is>
@@ -6460,11 +6461,7 @@
           <t>Chorus 1b (3) beginnt jetzt erst auf Takt 117,25 (Part in der Tabelle verschoben); der Blinder steht bis dahin voll</t>
         </is>
       </c>
-      <c r="D470" s="6" t="inlineStr">
-        <is>
-          <t>etwas zu früh -&gt; erst bei 117,25 wieder hiermit einsteigen</t>
-        </is>
-      </c>
+      <c r="D470" s="6" t="n"/>
       <c r="E470" s="6" t="n"/>
       <c r="F470" s="5" t="n"/>
       <c r="G470" s="5">
@@ -6477,7 +6474,7 @@
         </is>
       </c>
     </row>
-    <row r="471">
+    <row r="471" ht="187.2" customHeight="1">
       <c r="A471" s="4" t="n">
         <v>117.25</v>
       </c>
@@ -6493,11 +6490,7 @@
 Schnelle Einzelblitze in Rot, Orange, Gelb, Einsatz auf Takt 117,25. Drei kurze Blinder auf den Vierteln 120,5 / 120,75 / 121. Am Schluss drei Blinder triolisch (124 / 124,33 / 124,66); der letzte bleibt voll hell und klingt über 2 Takte ins Schluss-Schwarz aus.</t>
         </is>
       </c>
-      <c r="D471" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">erst hier wieder einsteigen </t>
-        </is>
-      </c>
+      <c r="D471" s="6" t="n"/>
       <c r="E471" s="6" t="n"/>
       <c r="F471" s="5" t="n"/>
       <c r="G471" s="5" t="n"/>
@@ -6657,11 +6650,7 @@
           <t>drei kurze Blinder auf 120,5 / 120,75 / 121 (bleiben wie sie sind)</t>
         </is>
       </c>
-      <c r="D484" s="6" t="inlineStr">
-        <is>
-          <t>hier sind 3 blinder, sind ok und könnmen hier bleiben</t>
-        </is>
-      </c>
+      <c r="D484" s="6" t="n"/>
       <c r="E484" s="6" t="n"/>
       <c r="F484" s="5" t="n"/>
       <c r="G484" s="5" t="n"/>
@@ -6833,11 +6822,7 @@
           <t>drei Blinder triolisch auf 124 / 124,33 / 124,66; der letzte steht bis zum Songende voll und klingt dann über 2 Takte (3,6 s) ins Schluss-Schwarz aus</t>
         </is>
       </c>
-      <c r="D498" s="6" t="inlineStr">
-        <is>
-          <t>hier müssten noch mal drei blinder hin, aber triolisch, also bei 124,0, 124,33, 124, 66. der letzte blinder bei 124,66 soll dann über 2 takte ausfaden</t>
-        </is>
-      </c>
+      <c r="D498" s="6" t="n"/>
       <c r="E498" s="6" t="n"/>
       <c r="F498" s="5" t="n"/>
       <c r="G498" s="5" t="n"/>
